--- a/Table_S6.xlsx
+++ b/Table_S6.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_S6_summary" sheetId="1" r:id="R40a21fbab12d4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Col0_ONSEN_locations" sheetId="2" r:id="R0d9614b2c6364dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49bp_locations" sheetId="3" r:id="R412f4412bfe04e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_definitions" sheetId="4" r:id="R1cd97e4c2ae74082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" r:id="R5292d9d7db5a4364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_S6_summary" sheetId="1" r:id="R3bad2cfb9c3b4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Col0_ONSEN_locations" sheetId="2" r:id="R47fae2b00d364fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49bp_locations" sheetId="3" r:id="Rfb26c1952d8a4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_definitions" sheetId="4" r:id="Rfb9585e521944a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" r:id="R0399dd9671d745ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -220,9 +220,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -374,10 +374,8 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HSF-family motif hits were filtered at relative PWM score &gt;= 0.85. Raw values represent PWM model-position hits. Non-redundant locations were obtained by merging genuinely overlapping HSF-family motif intervals across PWM models and strands. These locations represent computational motif compatibility, not experimentally verified HSF occupancy.</x:t>
-        </x:is>
+      <x:c r="A2" s="5" t="str">
+        <x:v>HSF-family motif hits were filtered at relative PWM score ≥0.85. Raw values represent PWM model-position hits. Non-redundant locations were obtained by merging genuinely overlapping HSF-family motif intervals across PWM models and strands. These locations represent computational motif compatibility, not experimentally verified HSF occupancy.</x:v>
       </x:c>
     </x:row>
     <x:row r="3"/>
@@ -455,12 +453,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="2" t="str">
-        <x:v>Native/designed 49-bp sequence</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">mutated</x:t>
-        </x:is>
+        <x:v>Native/designed HSE-disrupted 49-bp sequence</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>designed_HSE_disrupted</x:v>
       </x:c>
       <x:c r="C5" s="2" t="n"/>
       <x:c r="D5" s="2" t="n"/>
@@ -491,7 +487,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="2" t="str">
-        <x:v>Native/designed 49-bp sequence</x:v>
+        <x:v>Native/designed HSE-disrupted 49-bp sequence</x:v>
       </x:c>
       <x:c r="B6" s="2" t="inlineStr">
         <x:is>
@@ -11429,10 +11425,8 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Native_mutated_49bp</x:t>
-        </x:is>
+      <x:c r="A4" s="2" t="str">
+        <x:v>Native_designed_HSE_disrupted_49bp</x:v>
       </x:c>
       <x:c r="B4" s="2" t="inlineStr">
         <x:is>
@@ -11661,13 +11655,11 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Table title</x:t>
-        </x:is>
+      <x:c r="A4" s="2" t="str">
+        <x:v>Table title</x:v>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>Table S6. Non-redundant HSF-compatible locations in native and in-silico-designed HSE-disrupted 49-bp sequences and Col-0 ONSEN terminal candidate windows.</x:v>
+        <x:v>Table S6. Non-redundant HSF-compatible locations in the native and in-silico-designed HSE-disrupted 49-bp sequences and Col-0 ONSEN terminal candidate windows.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11688,10 +11680,8 @@
           <x:t xml:space="preserve">PWM threshold</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relative PWM score &gt;= 0.85.</x:t>
-        </x:is>
+      <x:c r="B6" s="2" t="str">
+        <x:v>Relative PWM score ≥0.85.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="4" customFormat="1" ht="28.799999237060547" customHeight="1">
@@ -11713,7 +11703,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="2" t="str">
-        <x:v>For the 49-bp native and designed sequences, motif_start and motif_end were already forward-sequence coordinates. For copy-wide ONSEN scans, reverse-strand positions were converted to forward-sequence coordinates before merging.</x:v>
+        <x:v>For the 49-bp native and designed HSE-disrupted sequences, motif_start and motif_end were already forward-sequence coordinates. For copy-wide ONSEN scans, reverse-strand positions were converted to forward-sequence coordinates before merging.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="4" customFormat="1" ht="28.799999237060547" customHeight="1">
@@ -11734,10 +11724,8 @@
           <x:t xml:space="preserve">Main result</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The native 49-bp sequence contained 31 HSF PWM model-position hits that collapsed into one non-redundant HSF-compatible location. Across the sixteen Col-0 ONSEN 800-bp terminal candidate windows, 48-75 raw HSF hits collapsed to 7-10 non-redundant locations per window.</x:t>
-        </x:is>
+      <x:c r="B10" s="2" t="str">
+        <x:v>The native 49-bp sequence contained 31 HSF PWM model-position hits that collapsed into one non-redundant HSF-compatible location. Across the sixteen Col-0 ONSEN 800-bp terminal candidate windows, 48–75 raw HSF hits collapsed to 7–10 non-redundant locations per window.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="4" customFormat="1" ht="28.799999237060547" customHeight="1">
